--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/13. technology_type.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/13. technology_type.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner\4. dml\1. skill_area [13-17,5]\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A28CD0-9984-4E61-A3D5-7C779EC0DDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2566D54A-95FB-4789-B3FB-0AADFF0BC0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/13. technology_type.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/13. technology_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2566D54A-95FB-4789-B3FB-0AADFF0BC0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D52CCD-B548-47D8-9CB1-40F43D41D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="72" yWindow="0" windowWidth="11448" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="technology_type" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="232">
   <si>
     <t>name</t>
   </si>
@@ -648,6 +648,120 @@
   </si>
   <si>
     <t xml:space="preserve">Colectie de functii si protocoale care faciliteaza comunicarea intre sisteme, gestionand conexiuni, socket‑uri, protocoale, request‑uri si transfer de date; exemple: Netty, Boost.Asio, Python </t>
+  </si>
+  <si>
+    <t>IDE</t>
+  </si>
+  <si>
+    <t>compilator</t>
+  </si>
+  <si>
+    <t>editor de cod</t>
+  </si>
+  <si>
+    <t>interpret de limbaj</t>
+  </si>
+  <si>
+    <t>debugger</t>
+  </si>
+  <si>
+    <t>profiler</t>
+  </si>
+  <si>
+    <t>tool analiză pachete rețea</t>
+  </si>
+  <si>
+    <t>tool terminal / shell</t>
+  </si>
+  <si>
+    <t>tool versionare cod</t>
+  </si>
+  <si>
+    <t>tool virtualizare</t>
+  </si>
+  <si>
+    <t>tool emulare</t>
+  </si>
+  <si>
+    <t>tool analiză cod dinamic</t>
+  </si>
+  <si>
+    <t>tool reverse engineering</t>
+  </si>
+  <si>
+    <t>tool pentesting</t>
+  </si>
+  <si>
+    <t>tool API gateway</t>
+  </si>
+  <si>
+    <t>tool load balancer</t>
+  </si>
+  <si>
+    <t>tool secret management</t>
+  </si>
+  <si>
+    <t>tool observability</t>
+  </si>
+  <si>
+    <t>tool API mocking</t>
+  </si>
+  <si>
+    <t>Un mediu de dezvoltare complet care integrează editor, debugger, build tools și unelte de analiză pentru scrierea și gestionarea codului.</t>
+  </si>
+  <si>
+    <t>Aplicație pentru scrierea și editarea codului, cu funcții precum evidențiere sintaxă, extensii și suport pentru limbaje.</t>
+  </si>
+  <si>
+    <t>Program care transformă codul sursă într-un executabil sau într-o formă optimizată pentru rulare.</t>
+  </si>
+  <si>
+    <t>Program ce execută codul direct, instrucțiune cu instrucțiune, fără a genera un fișier compilat.</t>
+  </si>
+  <si>
+    <t>Tool pentru analizarea și depanarea codului, permițând oprirea execuției și inspectarea variabilelor.</t>
+  </si>
+  <si>
+    <t>Tool pentru analiza performanței aplicațiilor ce măsurând consumul de resurse, timpul de execuție și identificând blocajele.</t>
+  </si>
+  <si>
+    <t>Tool pentru monitorizarea și inspectarea traficul de rețea la nivel de pachete pentru diagnosticare și securitate.</t>
+  </si>
+  <si>
+    <t>Interfață în linie de comandă pentru executarea comenzilor, scripturilor și administrarea sistemului.</t>
+  </si>
+  <si>
+    <t>Aplicație care gestionează versiuni ale codului sursă și interacționează cu sisteme precum Git.</t>
+  </si>
+  <si>
+    <t>Tool pentru crearea si gestionarea mașinilor virtuale ce permite rularea mai multor sisteme pe același hardware.</t>
+  </si>
+  <si>
+    <t>Tool pentru simularea hardware sau sisteme software pentru testare, dezvoltare sau compatibilitate.</t>
+  </si>
+  <si>
+    <t>Tool pentru analiza comportamentului unor aplicațiilor în timpul execuției pentru a detecta erori, scurgeri de memorie sau vulnerabilități.</t>
+  </si>
+  <si>
+    <t>Tool pentru examinarea unor programe compilate pentru a înțelege funcționarea, structura sau vulnerabilitățile lor.</t>
+  </si>
+  <si>
+    <t>Tool-uri folosite pentru testarea securității aplicațiilor și infrastructurii prin simularea atacurilor.</t>
+  </si>
+  <si>
+    <t>Tool-uri pentru geostionarea traficului către API-uri, oferind rutare, rate limiting, autentificare și monitorizare.</t>
+  </si>
+  <si>
+    <t>Tool-uri pentru distribuirea traficului între servere pentru a asigura performanță, disponibilitate și scalabilitate.</t>
+  </si>
+  <si>
+    <t>Tool-uri ce stochează și gestionează în siguranță secrete precum parole, tokenuri și chei de acces.</t>
+  </si>
+  <si>
+    <t>Tool-uri pentru colectarea si corelarea loguri, metricilor și trace-urilor pentru a monitoriza comportamentul aplicațiilor.</t>
+  </si>
+  <si>
+    <t>Tool-uri pentru generarea API-urilor simulate pentru testare, dezvoltare și izolare a componentelor fără backend real.</t>
   </si>
 </sst>
 </file>
@@ -1028,14 +1142,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C124"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="79.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5546875" customWidth="1"/>
+    <col min="2" max="2" width="79.109375" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1051,7 +1165,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>94</v>
       </c>
@@ -1060,7 +1174,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1068,7 +1182,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1076,7 +1190,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>95</v>
       </c>
@@ -1084,7 +1198,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>100</v>
       </c>
@@ -1092,7 +1206,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>96</v>
       </c>
@@ -1100,7 +1214,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -1108,7 +1222,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>98</v>
       </c>
@@ -1116,7 +1230,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1124,7 +1238,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -1132,7 +1246,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -1140,7 +1254,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1148,7 +1262,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1156,7 +1270,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1164,7 +1278,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
@@ -1172,7 +1286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1294,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
@@ -1188,7 +1302,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>103</v>
       </c>
@@ -1196,7 +1310,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>104</v>
       </c>
@@ -1204,7 +1318,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
@@ -1212,7 +1326,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
@@ -1220,7 +1334,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
@@ -1228,7 +1342,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
@@ -1236,7 +1350,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
@@ -1244,7 +1358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -1252,7 +1366,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -1260,7 +1374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
@@ -1268,7 +1382,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
@@ -1276,7 +1390,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
@@ -1284,7 +1398,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>21</v>
       </c>
@@ -1292,7 +1406,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
@@ -1300,7 +1414,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>37</v>
       </c>
@@ -1308,7 +1422,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>38</v>
       </c>
@@ -1316,7 +1430,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>39</v>
       </c>
@@ -1324,7 +1438,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
@@ -1332,7 +1446,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>105</v>
       </c>
@@ -1340,7 +1454,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>106</v>
       </c>
@@ -1348,7 +1462,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>41</v>
       </c>
@@ -1356,7 +1470,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>23</v>
       </c>
@@ -1364,7 +1478,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>24</v>
       </c>
@@ -1372,7 +1486,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>25</v>
       </c>
@@ -1380,7 +1494,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
@@ -1388,7 +1502,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>27</v>
       </c>
@@ -1396,7 +1510,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
@@ -1404,7 +1518,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>91</v>
       </c>
@@ -1412,7 +1526,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>42</v>
       </c>
@@ -1420,7 +1534,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>43</v>
       </c>
@@ -1428,7 +1542,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>44</v>
       </c>
@@ -1436,7 +1550,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>45</v>
       </c>
@@ -1444,7 +1558,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>46</v>
       </c>
@@ -1452,7 +1566,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>47</v>
       </c>
@@ -1460,7 +1574,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>48</v>
       </c>
@@ -1468,7 +1582,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>49</v>
       </c>
@@ -1476,7 +1590,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>50</v>
       </c>
@@ -1484,7 +1598,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>51</v>
       </c>
@@ -1492,7 +1606,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>52</v>
       </c>
@@ -1500,7 +1614,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>53</v>
       </c>
@@ -1508,7 +1622,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>55</v>
       </c>
@@ -1516,7 +1630,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>107</v>
       </c>
@@ -1524,7 +1638,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>56</v>
       </c>
@@ -1532,7 +1646,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>57</v>
       </c>
@@ -1540,7 +1654,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>58</v>
       </c>
@@ -1548,7 +1662,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>59</v>
       </c>
@@ -1556,7 +1670,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>108</v>
       </c>
@@ -1564,7 +1678,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>60</v>
       </c>
@@ -1572,7 +1686,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>61</v>
       </c>
@@ -1580,7 +1694,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>63</v>
       </c>
@@ -1588,7 +1702,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>64</v>
       </c>
@@ -1596,7 +1710,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>65</v>
       </c>
@@ -1604,7 +1718,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>66</v>
       </c>
@@ -1612,7 +1726,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>67</v>
       </c>
@@ -1620,7 +1734,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>68</v>
       </c>
@@ -1628,7 +1742,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>69</v>
       </c>
@@ -1636,7 +1750,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>70</v>
       </c>
@@ -1644,7 +1758,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>71</v>
       </c>
@@ -1652,7 +1766,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>72</v>
       </c>
@@ -1660,7 +1774,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>73</v>
       </c>
@@ -1668,7 +1782,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>75</v>
       </c>
@@ -1676,7 +1790,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>76</v>
       </c>
@@ -1684,7 +1798,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>77</v>
       </c>
@@ -1692,7 +1806,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>78</v>
       </c>
@@ -1700,7 +1814,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>79</v>
       </c>
@@ -1708,7 +1822,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>81</v>
       </c>
@@ -1716,7 +1830,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>82</v>
       </c>
@@ -1724,7 +1838,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>83</v>
       </c>
@@ -1732,7 +1846,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>84</v>
       </c>
@@ -1740,7 +1854,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>85</v>
       </c>
@@ -1748,7 +1862,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>86</v>
       </c>
@@ -1756,7 +1870,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>87</v>
       </c>
@@ -1764,7 +1878,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
         <v>88</v>
       </c>
@@ -1772,7 +1886,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>89</v>
       </c>
@@ -1780,7 +1894,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>74</v>
       </c>
@@ -1788,7 +1902,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>90</v>
       </c>
@@ -1796,7 +1910,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>80</v>
       </c>
@@ -1804,7 +1918,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>92</v>
       </c>
@@ -1812,13 +1926,186 @@
         <v>190</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
         <v>99</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>191</v>
       </c>
+    </row>
+    <row r="99" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="6"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="6"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="6"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="6"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="6"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="6"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/13. technology_type.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/13. technology_type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D52CCD-B548-47D8-9CB1-40F43D41D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24ABD2E-61C5-475D-93CA-A26797E35748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72" yWindow="0" windowWidth="11448" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="technology_type" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="216">
   <si>
     <t>name</t>
   </si>
@@ -659,51 +659,27 @@
     <t>editor de cod</t>
   </si>
   <si>
-    <t>interpret de limbaj</t>
-  </si>
-  <si>
-    <t>debugger</t>
-  </si>
-  <si>
-    <t>profiler</t>
-  </si>
-  <si>
     <t>tool analiză pachete rețea</t>
   </si>
   <si>
     <t>tool terminal / shell</t>
   </si>
   <si>
-    <t>tool versionare cod</t>
-  </si>
-  <si>
     <t>tool virtualizare</t>
   </si>
   <si>
     <t>tool emulare</t>
   </si>
   <si>
-    <t>tool analiză cod dinamic</t>
-  </si>
-  <si>
     <t>tool reverse engineering</t>
   </si>
   <si>
-    <t>tool pentesting</t>
-  </si>
-  <si>
     <t>tool API gateway</t>
   </si>
   <si>
     <t>tool load balancer</t>
   </si>
   <si>
-    <t>tool secret management</t>
-  </si>
-  <si>
-    <t>tool observability</t>
-  </si>
-  <si>
     <t>tool API mocking</t>
   </si>
   <si>
@@ -716,49 +692,25 @@
     <t>Program care transformă codul sursă într-un executabil sau într-o formă optimizată pentru rulare.</t>
   </si>
   <si>
-    <t>Program ce execută codul direct, instrucțiune cu instrucțiune, fără a genera un fișier compilat.</t>
-  </si>
-  <si>
-    <t>Tool pentru analizarea și depanarea codului, permițând oprirea execuției și inspectarea variabilelor.</t>
-  </si>
-  <si>
-    <t>Tool pentru analiza performanței aplicațiilor ce măsurând consumul de resurse, timpul de execuție și identificând blocajele.</t>
-  </si>
-  <si>
     <t>Tool pentru monitorizarea și inspectarea traficul de rețea la nivel de pachete pentru diagnosticare și securitate.</t>
   </si>
   <si>
     <t>Interfață în linie de comandă pentru executarea comenzilor, scripturilor și administrarea sistemului.</t>
   </si>
   <si>
-    <t>Aplicație care gestionează versiuni ale codului sursă și interacționează cu sisteme precum Git.</t>
-  </si>
-  <si>
     <t>Tool pentru crearea si gestionarea mașinilor virtuale ce permite rularea mai multor sisteme pe același hardware.</t>
   </si>
   <si>
     <t>Tool pentru simularea hardware sau sisteme software pentru testare, dezvoltare sau compatibilitate.</t>
   </si>
   <si>
-    <t>Tool pentru analiza comportamentului unor aplicațiilor în timpul execuției pentru a detecta erori, scurgeri de memorie sau vulnerabilități.</t>
-  </si>
-  <si>
     <t>Tool pentru examinarea unor programe compilate pentru a înțelege funcționarea, structura sau vulnerabilitățile lor.</t>
   </si>
   <si>
-    <t>Tool-uri folosite pentru testarea securității aplicațiilor și infrastructurii prin simularea atacurilor.</t>
-  </si>
-  <si>
     <t>Tool-uri pentru geostionarea traficului către API-uri, oferind rutare, rate limiting, autentificare și monitorizare.</t>
   </si>
   <si>
     <t>Tool-uri pentru distribuirea traficului între servere pentru a asigura performanță, disponibilitate și scalabilitate.</t>
-  </si>
-  <si>
-    <t>Tool-uri ce stochează și gestionează în siguranță secrete precum parole, tokenuri și chei de acces.</t>
-  </si>
-  <si>
-    <t>Tool-uri pentru colectarea si corelarea loguri, metricilor și trace-urilor pentru a monitoriza comportamentul aplicațiilor.</t>
   </si>
   <si>
     <t>Tool-uri pentru generarea API-urilor simulate pentru testare, dezvoltare și izolare a componentelor fără backend real.</t>
@@ -1142,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" customWidth="1"/>
@@ -1939,7 +1891,7 @@
         <v>194</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -1947,7 +1899,7 @@
         <v>196</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -1955,15 +1907,15 @@
         <v>195</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>197</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -1971,7 +1923,7 @@
         <v>198</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -1979,7 +1931,7 @@
         <v>199</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -1987,7 +1939,7 @@
         <v>200</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -1995,15 +1947,15 @@
         <v>201</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>202</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -2011,7 +1963,7 @@
         <v>203</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -2019,93 +1971,29 @@
         <v>204</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A110" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A111" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A113" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" s="6"/>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" s="6"/>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" s="6"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="6"/>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="6"/>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" s="6"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="6"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="6"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="6"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="6"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="6"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="6"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
